--- a/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SubRES_Tmpl/SubRES_Data_Centers_Trans.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DC details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DC details" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -537,19 +537,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>e_w82741307-225_FRA</t>
+          <t>e_VelikaGorica_HRV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>grid node -- way/82741307-225 (Paris, 21 km)</t>
+          <t>grid node -- way/89818719-400 (Zagreb, 17 km)</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1525</v>
+        <v>47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -560,19 +560,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>e_w110086345-400_FRA</t>
+          <t>e_Zagreb_HRV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>grid node -- way/110086345-400 (Nimes, 30 km)</t>
+          <t>grid node -- way/89820062-400 (Zagreb, 16 km)</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>304</v>
+        <v>10</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -593,19 +593,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>e_w24020601-400_FRA</t>
+          <t>e_Sesvete_HRV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>grid node -- way/24020601-400 (Lyon, 24 km)</t>
+          <t>grid node -- way/89819945-220 (Zagreb, 19 km)</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>242</v>
+        <v>5</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -624,19 +624,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>e_w222188543-400_FRA</t>
+          <t>e_Split_HRV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>grid node -- way/222188543-400 (Caen, 73 km)</t>
+          <t>grid node -- way/43337263-220 (Split, 11 km)</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -655,80 +655,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>e_w85605950-400_FRA</t>
+          <t>e_KastelStari_HRV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>grid node -- way/85605950-400 (Lille, 12 km)</t>
+          <t>grid node -- way/43337263-400 (Split, 11 km)</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>e_w235370803-400_FRA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>grid node -- way/235370803-400 (Bordeaux, 28 km)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>e_w146402374-225_FRA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>grid node -- way/146402374-225 (Strasbourg, 24 km)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>e_w207479669-225_FRA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>grid node -- way/207479669-225 (Pau, 62 km)</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>50</v>
-      </c>
-    </row>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>e_FR186-225_FRA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>grid node -- FR186-225 (Nice, 22 km)</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>32</v>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>~tfm_topins</t>
@@ -741,19 +686,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>e_w39389229-400_FRA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>grid node -- way/39389229-400 (Besancon, 51 km)</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>18</v>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>process</t>
@@ -805,19 +737,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>e_w753113423_FRA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>grid node -- way/753113423 (Caen, 11 km)</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>17</v>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>DC_1</t>
@@ -848,19 +767,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>e_w82825438-400_FRA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>grid node -- way/82825438-400 (Reims, 74 km)</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>17</v>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>DC_2</t>
@@ -891,19 +797,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>e_w312728271_FRA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>grid node -- way/312728271 (Perpignan, 8 km)</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>16</v>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>DC_3</t>
@@ -931,19 +824,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>e_w85710783-400_FRA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>grid node -- way/85710783-400 (Rouen, 24 km)</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12</v>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>DC_4</t>
@@ -974,19 +854,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>e_w179260933-400_FRA</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>grid node -- way/179260933-400 (Dijon, 25 km)</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>DC_5</t>
@@ -1010,35 +877,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>e_w83726363-225_FRA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>grid node -- way/83726363-225 (Clermont-Ferrand, 116 km)</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>6</v>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>e_w225210595-225_FRA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>grid node -- way/225210595-225 (Metz, 49 km)</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
       <c r="T18" s="1">
         <f>SUM(L12:T16)</f>
         <v/>
@@ -1049,35 +889,8 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>e_w83293593-225_FRA</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>grid node -- way/83293593-225 (Annecy, 30 km)</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>e_w111558550-400_FRA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>grid node -- way/111558550-400 (Bayonne, 9 km)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>~tfm_ins-TS: attribute=NCAP_AF; limtype=FX</t>
@@ -1085,19 +898,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>e_w146449309-400_FRA</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>grid node -- way/146449309-400 (Grenoble, 78 km)</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>process</t>
